--- a/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
+        <v>13:35</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13:35</v>
+        <v>22:41</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>רינת בר - 300 EP</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24455&amp;forum=music&amp;viewmode=all</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-24</v>
+        <v>2026-02-25</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>22:41</v>
+        <v>15:20</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רינת בר - 300 EP</v>
+        <v>אפרת גוש - לרדוף אחרי השמש</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-02-week04/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אפרת גוש - לרדוף אחרי השמש</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24456&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%a2%d7%95%d7%9e%d7%a8-%d7%90%d7%93%d7%9d-%d7%97%d7%9c%d7%a7-%d7%9e%d7%94%d7%a0%d7%a6%d7%97/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-25</v>
+        <v>2026-02-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>15:20</v>
+        <v>"משפחה וכבוד" הפותח את אלבומו העשירי  של עומר אדם מציב הצהרה אמנותית: זו אינה רק בלדת אהבה, אלא בלדה על מחיר ההצלחה. השיר יושב על קו התפר שבין עולם חומרי נוצץ לבין נאמנות פנימית, בין אהבה הרסנית לבין ערכי יסוד.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אפרת גוש - לרדוף אחרי השמש</v>
+        <v>עומר אדם – חלק מהנצח</v>
       </c>
     </row>
   </sheetData>
